--- a/templates/act-template.xlsx
+++ b/templates/act-template.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
   <si>
     <t>Общество с ограниченной ответственностью "Светлан Эстетикс"</t>
   </si>
@@ -142,13 +142,16 @@
     <t>должность</t>
   </si>
   <si>
+    <t>${signerPosition}</t>
+  </si>
+  <si>
     <t>подпись, ФИО</t>
   </si>
   <si>
     <t>${executorAuthorizedPerson}</t>
   </si>
   <si>
-    <t>${authorizedPerson}</t>
+    <t>${signerName}</t>
   </si>
 </sst>
 </file>
@@ -808,26 +811,26 @@
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="I28" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="I29" s="9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I31" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
